--- a/Excel-XLSX/UN-KRN.xlsx
+++ b/Excel-XLSX/UN-KRN.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>﻿"page"</t>
   </si>
@@ -27,100 +27,13 @@
     <t>maxPages</t>
   </si>
   <si>
-    <t>items</t>
-  </si>
-  <si>
-    <t>year</t>
-  </si>
-  <si>
-    <t>coo_id</t>
-  </si>
-  <si>
-    <t>coo_name</t>
-  </si>
-  <si>
-    <t>coo</t>
-  </si>
-  <si>
-    <t>coo_iso</t>
-  </si>
-  <si>
-    <t>coa_id</t>
-  </si>
-  <si>
-    <t>coa_name</t>
-  </si>
-  <si>
-    <t>coa</t>
-  </si>
-  <si>
-    <t>coa_iso</t>
-  </si>
-  <si>
-    <t>refugees</t>
-  </si>
-  <si>
-    <t>asylum_seekers</t>
-  </si>
-  <si>
-    <t>returned_refugees</t>
-  </si>
-  <si>
-    <t>idps</t>
-  </si>
-  <si>
-    <t>returned_idps</t>
-  </si>
-  <si>
-    <t>stateless</t>
-  </si>
-  <si>
-    <t>ooc</t>
-  </si>
-  <si>
-    <t>oip</t>
-  </si>
-  <si>
-    <t>hst</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
-    <t>3DUFiO</t>
-  </si>
-  <si>
-    <t>2015</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>Iraq</t>
-  </si>
-  <si>
-    <t>IRQ</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>Dem. People's Rep. of Korea</t>
-  </si>
-  <si>
-    <t>KRN</t>
-  </si>
-  <si>
-    <t>PRK</t>
+    <t>2nCq5l</t>
   </si>
   <si>
     <t>0</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -505,7 +418,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <sheetData>
     <row r="1">
@@ -518,130 +431,16 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="T2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Excel-XLSX/UN-KRN.xlsx
+++ b/Excel-XLSX/UN-KRN.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>﻿"page"</t>
   </si>
@@ -27,13 +27,100 @@
     <t>maxPages</t>
   </si>
   <si>
+    <t>items</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t>coo_id</t>
+  </si>
+  <si>
+    <t>coo_name</t>
+  </si>
+  <si>
+    <t>coo</t>
+  </si>
+  <si>
+    <t>coo_iso</t>
+  </si>
+  <si>
+    <t>coa_id</t>
+  </si>
+  <si>
+    <t>coa_name</t>
+  </si>
+  <si>
+    <t>coa</t>
+  </si>
+  <si>
+    <t>coa_iso</t>
+  </si>
+  <si>
+    <t>refugees</t>
+  </si>
+  <si>
+    <t>asylum_seekers</t>
+  </si>
+  <si>
+    <t>returned_refugees</t>
+  </si>
+  <si>
+    <t>idps</t>
+  </si>
+  <si>
+    <t>returned_idps</t>
+  </si>
+  <si>
+    <t>stateless</t>
+  </si>
+  <si>
+    <t>ooc</t>
+  </si>
+  <si>
+    <t>oip</t>
+  </si>
+  <si>
+    <t>hst</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
-    <t>2nCq5l</t>
+    <t>M2a6ut</t>
+  </si>
+  <si>
+    <t>2015</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>Iraq</t>
+  </si>
+  <si>
+    <t>IRQ</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>Dem. People's Rep. of Korea</t>
+  </si>
+  <si>
+    <t>KRN</t>
+  </si>
+  <si>
+    <t>PRK</t>
   </si>
   <si>
     <t>0</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
 </sst>
 </file>
@@ -418,7 +505,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:V2"/>
   <sheetFormatPr defaultRowHeight="12.85"/>
   <sheetData>
     <row r="1">
@@ -431,16 +518,130 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>22</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
